--- a/CompareKPI_United/template.xlsx
+++ b/CompareKPI_United/template.xlsx
@@ -1447,7 +1447,9 @@
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>首次acc&gt;0.2到最大acc：1.0~4.0s</t>
+          <t>ICE：&lt;=4s
+PHEV：&lt;=3.5s
+BEV：&lt;=3.5s</t>
         </is>
       </c>
       <c r="E9" s="16" t="n"/>
@@ -1469,7 +1471,9 @@
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad</t>
+          <t>ICE：sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad
+PHEV：sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad
+BEV：sqrt(1.0*R)-2 ~ sqrt(2.9*R)+2m/s；SetSpeed&lt;=sqrt(1.0*R)不判bad</t>
         </is>
       </c>
       <c r="E10" s="16" t="n"/>
@@ -1487,7 +1491,9 @@
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>&gt;=-2m/s2</t>
+          <t>ICE：&gt;=-2m/s2
+PHEV：&gt;=-2m/s2
+BEV：&gt;=-2m/s2</t>
         </is>
       </c>
       <c r="E11" s="16" t="n"/>
@@ -1505,7 +1511,9 @@
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>&gt;=-2m/s3</t>
+          <t>ICE：&gt;=-2m/s3
+PHEV：&gt;=-2m/s3
+BEV：&gt;=-2m/s3</t>
         </is>
       </c>
       <c r="E12" s="16" t="n"/>
@@ -1527,7 +1535,9 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>速度波动&lt;=1m/s</t>
+          <t>ICE：仪表车速极差&lt;=0.6km/h
+PHEV：仪表车速极差&lt;=0.3km/h
+BEV：仪表车速极差&lt;=0.3km/h</t>
         </is>
       </c>
       <c r="E13" s="16" t="n"/>
@@ -1545,7 +1555,9 @@
       <c r="C14" s="27" t="n"/>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>|加速度|&lt;=0.75m/s2</t>
+          <t>ICE：|加速度|&lt;=0.75m/s2
+PHEV：|加速度|&lt;=0.75m/s2
+BEV：|加速度|&lt;=0.75m/s2</t>
         </is>
       </c>
       <c r="E14" s="16" t="n"/>
@@ -1563,7 +1575,9 @@
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>|jerk|&lt;=1m/s3</t>
+          <t>ICE：|jerk|&lt;=1m/s3
+PHEV：|jerk|&lt;=1m/s3
+BEV：|jerk|&lt;=1m/s3</t>
         </is>
       </c>
       <c r="E15" s="16" t="n"/>
@@ -1603,7 +1617,9 @@
       <c r="C17" s="27" t="n"/>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>2~5m</t>
+          <t>ICE：3~4m
+PHEV：3~4m
+BEV：3~4m</t>
         </is>
       </c>
       <c r="E17" s="16" t="n"/>
@@ -1715,7 +1731,9 @@
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>1.0~2.5m/s3</t>
+          <t>ICE：最大jerk&lt;=1.5m/s3
+PHEV：最大jerk&lt;=1.5m/s3
+BEV：最大jerk&lt;=1.5m/s3</t>
         </is>
       </c>
       <c r="E23" s="19" t="n"/>
@@ -1831,7 +1849,9 @@
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="18" t="inlineStr">
         <is>
-          <t>1.0~2.5m/s3</t>
+          <t>ICE：最大jerk&lt;=2.5m/s3
+PHEV：最大jerk&lt;=2.5m/s3
+BEV：最大jerk&lt;=2.5m/s3</t>
         </is>
       </c>
       <c r="E29" s="19" t="n"/>
